--- a/04_regulatory-compliance-for-ai-eu-ai-act/demo/compliance_demo.xlsx
+++ b/04_regulatory-compliance-for-ai-eu-ai-act/demo/compliance_demo.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,6 +78,14 @@
       <i val="1"/>
       <color rgb="FF7F6000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -157,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -189,6 +197,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1105,6 +1116,21 @@
           <t>"Establish 15-day reporting SLA to national competent authority; integrate incident detection (from SP6 IR playbook) into the reporting pipeline; assign DPO + Compliance lead as joint owners"</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>"Stand up the Article 73 reporting workflow: 15-day SLA to the national competent authority (2 days for widespread-infringement incidents); wire in incident detection; define escalation and DPO + Compliance joint sign-off; rehearse before Aug 2026."</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>DPO + Compliance</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1525,74 +1551,74 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Conformity assessment, risk management, data governance, transparency, human oversight, accuracy, documentation, registration</t>
+          <t>Conformity assessment (Art 43), risk management system (Art 9), data governance (Art 10), technical documentation (Art 11), record-keeping (Art 12), transparency (Art 13), human oversight (Art 14), accuracy &amp; robustness (Art 15), registration (Art 49), post-market surveillance (Art 72)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="55" customHeight="1" s="11">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Limited Risk</t>
+          <t>GPAI / Foundation Models
+(Articles 51–55)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Transparency obligations.</t>
+          <t>General-Purpose AI models — including those with systemic risk.</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Chatbots, emotion recognition, deepfakes</t>
+          <t>Providers of general-purpose foundation models — e.g. models offered via API that power customer-facing assistants, chatbots, code copilots, RAG systems.</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Disclose AI usage to users.</t>
+          <t>Provider obligations — transparency to downstream deployers (Art. 53), copyright disclosure, technical documentation; if systemic risk, additional model evaluation + adversarial testing + Art. 55 obligations.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="55" customHeight="1" s="11">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>Limited Risk</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Transparency obligations.</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Chatbots, emotion recognition, deepfakes</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Disclose AI usage to users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1" s="11">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
           <t>Minimal Risk</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>No specific requirements.</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Spam filters, games, basic recommendations</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Voluntary codes of conduct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1" s="11">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>GPAI / Foundation Models
-(Articles 51–55)</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>General-Purpose AI models — including those with systemic risk.</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Providers of general-purpose foundation models — e.g. models offered via API that power customer-facing assistants, chatbots, code copilots, RAG systems.</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Provider obligations — transparency to downstream deployers (Art. 53), copyright disclosure, technical documentation; if systemic risk, additional model evaluation + adversarial testing + Art. 55 obligations.</t>
         </is>
       </c>
     </row>

--- a/04_regulatory-compliance-for-ai-eu-ai-act/demo/compliance_demo.xlsx
+++ b/04_regulatory-compliance-for-ai-eu-ai-act/demo/compliance_demo.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>EU AI Act (direct), GDPR, UK AI framework. WarehouseWatch and HireBot = High-Risk under Annex III; AssistGPT = GPAI under Articles 51–55. Article 73 (serious-incident reporting) enforces from August 2026 for High-Risk systems.</t>
+          <t>EU AI Act (direct), GDPR, UK AI framework. WarehouseWatch and HireBot = High-Risk under Annex III; AssistGPT = GPAI under Articles 51–55. Article 73 (serious-incident reporting) applies from 2 December 2027 for stand-alone Annex III High-Risk systems, deferred from 2 August 2026 by Regulation (EU) 2026/1744.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Serious-Incident Reporting — Notify authorities of serious incidents per Article 73 (enforces Aug 2026)</t>
+          <t>Serious-Incident Reporting — Notify authorities of serious incidents per Article 73 (applies 2 Dec 2027)</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1103,7 +1103,7 @@
       <c r="F8" s="8" t="inlineStr">
         <is>
           <t>"Gap"
-Reasoning: No reporting workflow exists. Article 73 enforces from August 2026 for all High-Risk systems; without a documented incident-detection-and-reporting pipeline, the company will be non-compliant on day one of enforcement.</t>
+Reasoning: No reporting workflow exists. Article 73 applies from 2 December 2027 for stand-alone Annex III High-Risk systems; without a documented incident-detection-and-reporting pipeline, the company will be non-compliant on day one of enforcement.</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>"Stand up the Article 73 reporting workflow: 15-day SLA to the national competent authority (2 days for widespread-infringement incidents); wire in incident detection; define escalation and DPO + Compliance joint sign-off; rehearse before Aug 2026."</t>
+          <t>"Stand up the Article 73 reporting workflow: 15-day SLA to the national competent authority (2 days for widespread-infringement incidents); wire in incident detection; define escalation and DPO + Compliance joint sign-off; rehearse before 2 Dec 2027."</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
